--- a/rmonize/data_proc_elem/DPE_CARLA_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_CARLA_P1.xlsx
@@ -2765,27 +2765,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SALT_BISCUIT_0605</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -3115,27 +3120,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MUTTON_LAMB_070104</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -3590,27 +3600,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RABBIT_070205</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -5420,27 +5435,32 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>COFFEE_IMITATE_130304</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -6335,27 +6355,32 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CONDIMENTS_1504</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
